--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -5837,7 +5837,7 @@
         <v>136091903</v>
       </c>
       <c r="B46" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136092022</v>
       </c>
       <c r="B47" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>136091964</v>
       </c>
       <c r="B59" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>136091947</v>
       </c>
       <c r="B60" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -5837,7 +5837,7 @@
         <v>136091903</v>
       </c>
       <c r="B46" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136092022</v>
       </c>
       <c r="B47" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>136091964</v>
       </c>
       <c r="B59" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>136091947</v>
       </c>
       <c r="B60" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>76137224</v>
+        <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>87300</v>
+        <v>97590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,41 +1428,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>454</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rovspindling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius napus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lönnsvadberget, Söderbärke, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534995</v>
+        <v>535072</v>
       </c>
       <c r="R8" t="n">
-        <v>6671741</v>
+        <v>6671852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1489,17 +1482,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Medexkurenter var även Sören Gutén och Magnus Gustafsson</t>
+          <t>Rikligt på den murkna lågan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,82 +1511,78 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Rikmarkspåverkan</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Janols</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Janols, Janolof Hermansson, Uno Skog</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76137224</t>
+          <t>https://artportalen.se/Sighting/136976807</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119294187</v>
+        <v>76137224</v>
       </c>
       <c r="B9" t="n">
-        <v>93199</v>
+        <v>87300</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>788</v>
+        <v>454</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Rovspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius napus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Lönnsvadberget, Söderbärke, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534878</v>
+        <v>534995</v>
       </c>
       <c r="R9" t="n">
-        <v>6671746</v>
+        <v>6671741</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,12 +1606,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Medexkurenter var även Sören Gutén och Magnus Gustafsson</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,81 +1625,82 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Rikmarkspåverkan</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Anders Janols</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Anders Janols, Janolof Hermansson, Uno Skog</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294187</t>
+          <t>https://artportalen.se/Sighting/76137224</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67601773</v>
+        <v>119294187</v>
       </c>
       <c r="B10" t="n">
-        <v>92147</v>
+        <v>93199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1101</v>
+        <v>788</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534899</v>
+        <v>534878</v>
       </c>
       <c r="R10" t="n">
-        <v>6671788</v>
+        <v>6671746</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1719,12 +1724,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-09-17</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-09-17</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,59 +1738,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>mossig barrskog med gamla tallar</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>på rotben # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67601773</t>
+          <t>https://artportalen.se/Sighting/119294187</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109971242</v>
+        <v>67601773</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>92147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,37 +1772,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1101</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534809</v>
+        <v>534899</v>
       </c>
       <c r="R11" t="n">
-        <v>6671806</v>
+        <v>6671788</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1850,12 +1836,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2017-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2017-09-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1870,17 +1856,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>naturskog</t>
+          <t>mossig barrskog med gamla tallar</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>på rotben # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1891,19 +1887,19 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Bengt Lundborg</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109971242</t>
+          <t>https://artportalen.se/Sighting/67601773</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121853326</v>
+        <v>109971242</v>
       </c>
       <c r="B12" t="n">
         <v>91909</v>
@@ -1932,19 +1928,22 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534960</v>
+        <v>534809</v>
       </c>
       <c r="R12" t="n">
-        <v>6671792</v>
+        <v>6671806</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1968,17 +1967,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gysinge Skog naturvärdesbedömning.</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,38 +1981,49 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>gammal barrblandskog med tjock mossmatta</t>
+          <t>naturskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Janolof Hermansson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121853326</t>
+          <t>https://artportalen.se/Sighting/109971242</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>75213796</v>
+        <v>121853326</v>
       </c>
       <c r="B13" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,40 +2031,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535024</v>
+        <v>534960</v>
       </c>
       <c r="R13" t="n">
-        <v>6671800</v>
+        <v>6671792</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2083,12 +2085,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2018-12-08</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2018-12-08</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,56 +2104,35 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>naturskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>granlåga # Picea abies</t>
+          <t>gammal barrblandskog med tjock mossmatta</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75213796</t>
+          <t>https://artportalen.se/Sighting/121853326</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119983043</v>
+        <v>75213796</v>
       </c>
       <c r="B14" t="n">
         <v>92369</v>
@@ -2180,14 +2166,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535007</v>
+        <v>535024</v>
       </c>
       <c r="R14" t="n">
-        <v>6671754</v>
+        <v>6671800</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2214,12 +2200,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2018-12-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2018-12-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2252,14 +2238,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2270,19 +2251,19 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119983043</t>
+          <t>https://artportalen.se/Sighting/75213796</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119984203</v>
+        <v>119983043</v>
       </c>
       <c r="B15" t="n">
         <v>92369</v>
@@ -2320,10 +2301,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534913</v>
+        <v>535007</v>
       </c>
       <c r="R15" t="n">
-        <v>6671750</v>
+        <v>6671754</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2378,6 +2359,26 @@
           <t>naturskog</t>
         </is>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2392,13 +2393,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119984203</t>
+          <t>https://artportalen.se/Sighting/119983043</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121853325</v>
+        <v>119984203</v>
       </c>
       <c r="B16" t="n">
         <v>92369</v>
@@ -2427,19 +2428,22 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534960</v>
+        <v>534913</v>
       </c>
       <c r="R16" t="n">
-        <v>6671792</v>
+        <v>6671750</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2463,17 +2467,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gysinge Skog naturvärdesbedömning.</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2482,88 +2481,82 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>gammal barrblandskog med tjock mossmatta</t>
+          <t>naturskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121853325</t>
+          <t>https://artportalen.se/Sighting/119984203</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129846293</v>
+        <v>121853325</v>
       </c>
       <c r="B17" t="n">
-        <v>96708</v>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535006</v>
+        <v>534960</v>
       </c>
       <c r="R17" t="n">
-        <v>6671790</v>
+        <v>6671792</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2587,12 +2580,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,49 +2599,38 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>marken</t>
+          <t>gammal barrblandskog med tjock mossmatta</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129846293</t>
+          <t>https://artportalen.se/Sighting/121853325</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126301457</v>
+        <v>129846293</v>
       </c>
       <c r="B18" t="n">
-        <v>97231</v>
+        <v>96708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,31 +2638,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2683,14 +2670,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>534778</v>
+        <v>535006</v>
       </c>
       <c r="R18" t="n">
-        <v>6671654</v>
+        <v>6671790</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2717,12 +2704,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2737,7 +2724,17 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>marken</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2754,16 +2751,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126301457</t>
+          <t>https://artportalen.se/Sighting/129846293</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127819880</v>
+        <v>126301457</v>
       </c>
       <c r="B19" t="n">
-        <v>92632</v>
+        <v>97231</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,40 +2768,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535002</v>
+        <v>534778</v>
       </c>
       <c r="R19" t="n">
-        <v>6671760</v>
+        <v>6671654</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2828,12 +2834,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2846,47 +2852,32 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127819880</t>
+          <t>https://artportalen.se/Sighting/126301457</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129846284</v>
+        <v>127819880</v>
       </c>
       <c r="B20" t="n">
         <v>92632</v>
@@ -2920,17 +2911,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>534990</v>
+        <v>535002</v>
       </c>
       <c r="R20" t="n">
-        <v>6671767</v>
+        <v>6671760</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2954,12 +2945,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2972,16 +2963,6 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3005,76 +2986,68 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129846284</t>
+          <t>https://artportalen.se/Sighting/127819880</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127820111</v>
+        <v>129846284</v>
       </c>
       <c r="B21" t="n">
-        <v>93215</v>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4368</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>535006</v>
+        <v>534990</v>
       </c>
       <c r="R21" t="n">
-        <v>6671736</v>
+        <v>6671767</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3098,12 +3071,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3116,68 +3089,109 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127820111</t>
+          <t>https://artportalen.se/Sighting/129846284</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119294755</v>
+        <v>127820111</v>
       </c>
       <c r="B22" t="n">
-        <v>92869</v>
+        <v>93215</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534906</v>
+        <v>535006</v>
       </c>
       <c r="R22" t="n">
-        <v>6671703</v>
+        <v>6671736</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3201,12 +3215,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3215,30 +3229,31 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294755</t>
+          <t>https://artportalen.se/Sighting/127820111</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119889108</v>
+        <v>119294755</v>
       </c>
       <c r="B23" t="n">
         <v>92869</v>
@@ -3266,26 +3281,17 @@
           <t>(Scop.) Fr.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534842</v>
+        <v>534906</v>
       </c>
       <c r="R23" t="n">
-        <v>6671768</v>
+        <v>6671703</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3312,22 +3318,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3342,27 +3338,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889108</t>
+          <t>https://artportalen.se/Sighting/119294755</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121853351</v>
+        <v>119889108</v>
       </c>
       <c r="B24" t="n">
-        <v>91872</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3370,34 +3366,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>535076</v>
+        <v>534842</v>
       </c>
       <c r="R24" t="n">
-        <v>6671855</v>
+        <v>6671768</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3424,17 +3429,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gysinge Skog naturvärdesbedömning.</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3445,87 +3455,69 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>äldre granskog med tjock mossmatta</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121853351</t>
+          <t>https://artportalen.se/Sighting/119889108</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109971233</v>
+        <v>121853351</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534809</v>
+        <v>535076</v>
       </c>
       <c r="R25" t="n">
-        <v>6671806</v>
+        <v>6671855</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3549,17 +3541,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>hackspår i gammal gran</t>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3570,28 +3562,38 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>äldre granskog med tjock mossmatta</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Bengt Lundborg</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109971233</t>
+          <t>https://artportalen.se/Sighting/121853351</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121853330</v>
+        <v>109971233</v>
       </c>
       <c r="B26" t="n">
         <v>57953</v>
@@ -3620,24 +3622,27 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534807</v>
+        <v>534809</v>
       </c>
       <c r="R26" t="n">
-        <v>6671801</v>
+        <v>6671806</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3661,17 +3666,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gysinge Skog naturvärdesbedömning.</t>
+          <t>hackspår i gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3682,76 +3687,71 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>gammal barrblandskog med tjock mossmatta</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Janolof Hermansson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121853330</t>
+          <t>https://artportalen.se/Sighting/109971233</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119889464</v>
+        <v>121853330</v>
       </c>
       <c r="B27" t="n">
-        <v>99035</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534747</v>
+        <v>534807</v>
       </c>
       <c r="R27" t="n">
-        <v>6671800</v>
+        <v>6671801</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3778,22 +3778,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3804,74 +3799,84 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog med tjock mossmatta</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889464</t>
+          <t>https://artportalen.se/Sighting/121853330</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>88075747</v>
+        <v>136976803</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>58008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gölbäcken Smedjebacken, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534996</v>
+        <v>534873</v>
       </c>
       <c r="R28" t="n">
-        <v>6671715</v>
+        <v>6671716</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3898,22 +3903,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-09-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-09-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bedömdes som äldre hackspår, troligen från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3922,84 +3932,79 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lena Stigsdotter</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lena Stigsdotter</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88075747</t>
+          <t>https://artportalen.se/Sighting/136976803</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109971207</v>
+        <v>136976804</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>58008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534791</v>
+        <v>534931</v>
       </c>
       <c r="R29" t="n">
-        <v>6671816</v>
+        <v>6671791</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4023,12 +4028,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bedöms som äldre hackspår, troligen frän tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4037,79 +4057,68 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>naturskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Bengt Lundborg</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109971207</t>
+          <t>https://artportalen.se/Sighting/136976804</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119294425</v>
+        <v>119889464</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534910</v>
+        <v>534747</v>
       </c>
       <c r="R30" t="n">
-        <v>6671796</v>
+        <v>6671800</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4136,12 +4145,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4156,24 +4175,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294425</t>
+          <t>https://artportalen.se/Sighting/119889464</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119295534</v>
+        <v>88075747</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -4201,20 +4220,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken Smedjebacken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534987</v>
+        <v>534996</v>
       </c>
       <c r="R31" t="n">
-        <v>6671767</v>
+        <v>6671715</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4238,12 +4265,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2020-09-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2020-09-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4252,30 +4289,31 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Lena Stigsdotter</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Lena Stigsdotter</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119295534</t>
+          <t>https://artportalen.se/Sighting/88075747</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119295577</v>
+        <v>109971207</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -4303,20 +4341,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534982</v>
+        <v>534791</v>
       </c>
       <c r="R32" t="n">
-        <v>6671760</v>
+        <v>6671816</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4340,12 +4390,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4354,30 +4404,41 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>naturskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Janolof Hermansson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119295577</t>
+          <t>https://artportalen.se/Sighting/109971207</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119295583</v>
+        <v>119294425</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4412,10 +4473,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>534962</v>
+        <v>534910</v>
       </c>
       <c r="R33" t="n">
-        <v>6671760</v>
+        <v>6671796</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4473,13 +4534,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119295583</t>
+          <t>https://artportalen.se/Sighting/119294425</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119888281</v>
+        <v>119295534</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4510,14 +4571,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>534939</v>
+        <v>534987</v>
       </c>
       <c r="R34" t="n">
-        <v>6671725</v>
+        <v>6671767</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4544,22 +4605,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4574,24 +4625,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119888281</t>
+          <t>https://artportalen.se/Sighting/119295534</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119888431</v>
+        <v>119295577</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4622,17 +4673,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>534953</v>
+        <v>534982</v>
       </c>
       <c r="R35" t="n">
-        <v>6671754</v>
+        <v>6671760</v>
       </c>
       <c r="S35" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4656,27 +4707,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Knärot precis invid markeringen för avverkning vägen genom nyckelbiotopen.</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4691,24 +4727,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119888431</t>
+          <t>https://artportalen.se/Sighting/119295577</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119889221</v>
+        <v>119295583</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4737,21 +4773,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>534821</v>
+        <v>534962</v>
       </c>
       <c r="R36" t="n">
-        <v>6671773</v>
+        <v>6671760</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4778,22 +4809,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4808,24 +4829,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889221</t>
+          <t>https://artportalen.se/Sighting/119295583</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119889427</v>
+        <v>119888281</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4856,14 +4877,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>534759</v>
+        <v>534939</v>
       </c>
       <c r="R37" t="n">
-        <v>6671790</v>
+        <v>6671725</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4895,7 +4916,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4905,7 +4926,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4931,13 +4952,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889427</t>
+          <t>https://artportalen.se/Sighting/119888281</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119889540</v>
+        <v>119888431</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4968,17 +4989,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>534957</v>
+        <v>534953</v>
       </c>
       <c r="R38" t="n">
-        <v>6671726</v>
+        <v>6671754</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5007,7 +5028,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5017,7 +5038,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Knärot precis invid markeringen för avverkning vägen genom nyckelbiotopen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5032,24 +5058,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889540</t>
+          <t>https://artportalen.se/Sighting/119888431</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119889607</v>
+        <v>119889221</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -5078,19 +5104,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>534983</v>
+        <v>534821</v>
       </c>
       <c r="R39" t="n">
-        <v>6671688</v>
+        <v>6671773</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5119,7 +5150,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +5160,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5144,24 +5175,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889607</t>
+          <t>https://artportalen.se/Sighting/119889221</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119927799</v>
+        <v>119889427</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -5190,23 +5221,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>534969</v>
+        <v>534759</v>
       </c>
       <c r="R40" t="n">
-        <v>6671737</v>
+        <v>6671790</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5233,42 +5260,51 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119927799</t>
+          <t>https://artportalen.se/Sighting/119889427</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119927817</v>
+        <v>119889540</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5297,23 +5333,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>534963</v>
+        <v>534957</v>
       </c>
       <c r="R41" t="n">
-        <v>6671740</v>
+        <v>6671726</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5340,42 +5372,51 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119927817</t>
+          <t>https://artportalen.se/Sighting/119889540</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121853329</v>
+        <v>119889607</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5406,17 +5447,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>534801</v>
+        <v>534983</v>
       </c>
       <c r="R42" t="n">
-        <v>6671794</v>
+        <v>6671688</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5440,17 +5481,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gysinge Skog naturvärdesbedömning.</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5461,33 +5507,28 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>gammal barrblandskog med tjock mossmatta</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121853329</t>
+          <t>https://artportalen.se/Sighting/119889607</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125831076</v>
+        <v>119927799</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5522,14 +5563,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>534962</v>
+        <v>534969</v>
       </c>
       <c r="R43" t="n">
-        <v>6671779</v>
+        <v>6671737</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5556,12 +5597,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5574,37 +5615,27 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>grov mossig granlåga</t>
-        </is>
-      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125831076</t>
+          <t>https://artportalen.se/Sighting/119927799</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127819624</v>
+        <v>119927817</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5632,32 +5663,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>535048</v>
+        <v>534963</v>
       </c>
       <c r="R44" t="n">
-        <v>6671847</v>
+        <v>6671740</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5681,12 +5704,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5702,24 +5725,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127819624</t>
+          <t>https://artportalen.se/Sighting/119927817</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127819733</v>
+        <v>121853329</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5747,32 +5770,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>535016</v>
+        <v>534801</v>
       </c>
       <c r="R45" t="n">
-        <v>6671800</v>
+        <v>6671794</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5796,12 +5807,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5810,34 +5826,38 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog med tjock mossmatta</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127819733</t>
+          <t>https://artportalen.se/Sighting/121853329</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136091903</v>
+        <v>125831076</v>
       </c>
       <c r="B46" t="n">
-        <v>99346</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5869,14 +5889,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>534757</v>
+        <v>534962</v>
       </c>
       <c r="R46" t="n">
-        <v>6671803</v>
+        <v>6671779</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5903,12 +5923,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5923,7 +5943,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>grov mossig granlåga</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5934,22 +5959,22 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136091903</t>
+          <t>https://artportalen.se/Sighting/125831076</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136092022</v>
+        <v>127819624</v>
       </c>
       <c r="B47" t="n">
-        <v>99346</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5976,7 +6001,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5989,17 +6014,17 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>534973</v>
+        <v>535048</v>
       </c>
       <c r="R47" t="n">
-        <v>6671751</v>
+        <v>6671847</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6023,17 +6048,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>tre ynkliga plantor. Verkar vara hämmade av torkan. Platsen snitslad som hänsynsyta på radie av 8 meter.</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6046,77 +6066,80 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136092022</t>
+          <t>https://artportalen.se/Sighting/127819624</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125830803</v>
+        <v>127819733</v>
       </c>
       <c r="B48" t="n">
-        <v>102241</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>534901</v>
+        <v>535016</v>
       </c>
       <c r="R48" t="n">
-        <v>6671688</v>
+        <v>6671800</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6140,12 +6163,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6158,73 +6181,69 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830803</t>
+          <t>https://artportalen.se/Sighting/127819733</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>67601802</v>
+        <v>136091903</v>
       </c>
       <c r="B49" t="n">
-        <v>97983</v>
+        <v>99346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>534847</v>
+        <v>534757</v>
       </c>
       <c r="R49" t="n">
-        <v>6671789</v>
+        <v>6671803</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6251,12 +6270,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2017-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2017-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6265,17 +6284,13 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>litet klibbalkärr</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6292,54 +6307,66 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67601802</t>
+          <t>https://artportalen.se/Sighting/136091903</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119294603</v>
+        <v>136092022</v>
       </c>
       <c r="B50" t="n">
-        <v>104628</v>
+        <v>99346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>534885</v>
+        <v>534973</v>
       </c>
       <c r="R50" t="n">
-        <v>6671725</v>
+        <v>6671751</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6363,12 +6390,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>tre ynkliga plantor. Verkar vara hämmade av torkan. Platsen snitslad som hänsynsyta på radie av 8 meter.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6377,72 +6409,83 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294603</t>
+          <t>https://artportalen.se/Sighting/136092022</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125830603</v>
+        <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>104628</v>
+        <v>99353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>535006</v>
+        <v>534941</v>
       </c>
       <c r="R51" t="n">
-        <v>6671720</v>
+        <v>6671780</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6469,12 +6512,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Cirka 30 m till hyggesgräns. På liten yta 2x2. dm</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6483,66 +6541,55 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>nära bäcken</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830603</t>
+          <t>https://artportalen.se/Sighting/136976805</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125830789</v>
+        <v>125830803</v>
       </c>
       <c r="B52" t="n">
-        <v>104628</v>
+        <v>102241</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6623,16 +6670,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830789</t>
+          <t>https://artportalen.se/Sighting/125830803</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118074415</v>
+        <v>67601802</v>
       </c>
       <c r="B53" t="n">
-        <v>101326</v>
+        <v>97983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,38 +6687,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Knapptjärn, Dlr</t>
+          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>534955</v>
+        <v>534847</v>
       </c>
       <c r="R53" t="n">
-        <v>6671722</v>
+        <v>6671789</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6698,12 +6744,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2017-09-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2017-09-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6712,34 +6758,43 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>litet klibbalkärr</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Åke Persson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118074415</t>
+          <t>https://artportalen.se/Sighting/67601802</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119057996</v>
+        <v>119294603</v>
       </c>
       <c r="B54" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6747,41 +6802,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gölbäcken - Kapptjärn, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>534905</v>
+        <v>534885</v>
       </c>
       <c r="R54" t="n">
-        <v>6671685</v>
+        <v>6671725</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6805,12 +6856,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6819,39 +6870,33 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119057996</t>
+          <t>https://artportalen.se/Sighting/119294603</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119294689</v>
+        <v>125830603</v>
       </c>
       <c r="B55" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6859,37 +6904,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>534895</v>
+        <v>535006</v>
       </c>
       <c r="R55" t="n">
-        <v>6671684</v>
+        <v>6671720</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6913,12 +6962,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6927,33 +6976,44 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>nära bäcken</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294689</t>
+          <t>https://artportalen.se/Sighting/125830603</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119927788</v>
+        <v>125830789</v>
       </c>
       <c r="B56" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6961,21 +7021,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6985,14 +7045,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>534956</v>
+        <v>534901</v>
       </c>
       <c r="R56" t="n">
-        <v>6671735</v>
+        <v>6671688</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7019,12 +7079,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7037,30 +7097,35 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119927788</t>
+          <t>https://artportalen.se/Sighting/125830789</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125830768</v>
+        <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>101326</v>
+        <v>104876</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7068,38 +7133,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>534901</v>
+        <v>534873</v>
       </c>
       <c r="R57" t="n">
-        <v>6671688</v>
+        <v>6671716</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7126,12 +7187,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kvar på hygge som torkar ut.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7140,39 +7216,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830768</t>
+          <t>https://artportalen.se/Sighting/136976802</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126301498</v>
+        <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>101326</v>
+        <v>104876</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7180,41 +7250,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>534879</v>
+        <v>534986</v>
       </c>
       <c r="R58" t="n">
-        <v>6671662</v>
+        <v>6671759</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7238,17 +7304,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Inom kulturmijöhänsyn</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7257,39 +7328,33 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126301498</t>
+          <t>https://artportalen.se/Sighting/136976806</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136091964</v>
+        <v>118074415</v>
       </c>
       <c r="B59" t="n">
-        <v>101556</v>
+        <v>101326</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7321,14 +7386,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>534902</v>
+        <v>534955</v>
       </c>
       <c r="R59" t="n">
-        <v>6671682</v>
+        <v>6671722</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7355,12 +7420,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7373,35 +7438,30 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136091964</t>
+          <t>https://artportalen.se/Sighting/118074415</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136091947</v>
+        <v>119057996</v>
       </c>
       <c r="B60" t="n">
-        <v>99623</v>
+        <v>101326</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7409,21 +7469,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7433,14 +7493,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken - Kapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>534900</v>
+        <v>534905</v>
       </c>
       <c r="R60" t="n">
-        <v>6671688</v>
+        <v>6671685</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7467,12 +7527,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7487,7 +7547,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7498,22 +7558,22 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136091947</t>
+          <t>https://artportalen.se/Sighting/119057996</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126301411</v>
+        <v>119294689</v>
       </c>
       <c r="B61" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7521,37 +7581,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>534748</v>
+        <v>534895</v>
       </c>
       <c r="R61" t="n">
-        <v>6671807</v>
+        <v>6671684</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7575,12 +7635,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7589,39 +7649,33 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126301411</t>
+          <t>https://artportalen.se/Sighting/119294689</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126301477</v>
+        <v>119927788</v>
       </c>
       <c r="B62" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7629,19 +7683,23 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -7649,14 +7707,14 @@
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>534789</v>
+        <v>534956</v>
       </c>
       <c r="R62" t="n">
-        <v>6671626</v>
+        <v>6671735</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7683,17 +7741,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7706,24 +7759,693 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119927788</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125830768</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>534901</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Åke Persson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830768</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126301498</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>534879</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6671662</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Inom kulturmijöhänsyn</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126301498</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136091964</v>
+      </c>
+      <c r="B65" t="n">
+        <v>101556</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>534902</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6671682</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136091964</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136091947</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99623</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>534900</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136091947</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126301411</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>534748</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6671807</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126301411</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126301477</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>534789</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6671626</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126301477</t>
         </is>
@@ -7792,6 +8514,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>136976803</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>136976804</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>136976803</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>136976804</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -3861,11 +3861,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3986,11 +3982,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>136976803</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>136976804</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>136976803</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>136976804</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>136976803</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>136976804</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -7117,7 +7117,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>136976805</v>
       </c>
       <c r="B51" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>136976802</v>
       </c>
       <c r="B57" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>136976806</v>
       </c>
       <c r="B58" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ68"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>75213796</v>
+        <v>137471394</v>
       </c>
       <c r="B14" t="n">
-        <v>92369</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,40 +2143,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
+          <t>Gladtjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535024</v>
+        <v>534808</v>
       </c>
       <c r="R14" t="n">
-        <v>6671800</v>
+        <v>6671802</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2200,12 +2197,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2018-12-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2018-12-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2214,56 +2211,40 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>naturskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>granlåga # Picea abies</t>
+          <t>förrötad granlåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75213796</t>
+          <t>https://artportalen.se/Sighting/137471394</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119983043</v>
+        <v>75213796</v>
       </c>
       <c r="B15" t="n">
         <v>92369</v>
@@ -2297,14 +2278,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535007</v>
+        <v>535024</v>
       </c>
       <c r="R15" t="n">
-        <v>6671754</v>
+        <v>6671800</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2331,12 +2312,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2018-12-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2018-12-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,14 +2350,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2387,19 +2363,19 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119983043</t>
+          <t>https://artportalen.se/Sighting/75213796</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119984203</v>
+        <v>119983043</v>
       </c>
       <c r="B16" t="n">
         <v>92369</v>
@@ -2437,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534913</v>
+        <v>535007</v>
       </c>
       <c r="R16" t="n">
-        <v>6671750</v>
+        <v>6671754</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2495,6 +2471,26 @@
           <t>naturskog</t>
         </is>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
@@ -2509,13 +2505,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119984203</t>
+          <t>https://artportalen.se/Sighting/119983043</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121853325</v>
+        <v>119984203</v>
       </c>
       <c r="B17" t="n">
         <v>92369</v>
@@ -2544,19 +2540,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>534960</v>
+        <v>534913</v>
       </c>
       <c r="R17" t="n">
-        <v>6671792</v>
+        <v>6671750</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2580,17 +2579,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gysinge Skog naturvärdesbedömning.</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,88 +2593,82 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>gammal barrblandskog med tjock mossmatta</t>
+          <t>naturskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Cecilia Rastad, Åke Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121853325</t>
+          <t>https://artportalen.se/Sighting/119984203</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129846293</v>
+        <v>121853325</v>
       </c>
       <c r="B18" t="n">
-        <v>96708</v>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535006</v>
+        <v>534960</v>
       </c>
       <c r="R18" t="n">
-        <v>6671790</v>
+        <v>6671792</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2704,12 +2692,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2718,99 +2711,76 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>marken</t>
+          <t>gammal barrblandskog med tjock mossmatta</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129846293</t>
+          <t>https://artportalen.se/Sighting/121853325</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126301457</v>
+        <v>137471387</v>
       </c>
       <c r="B19" t="n">
-        <v>97231</v>
+        <v>92617</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gladtjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534778</v>
+        <v>534878</v>
       </c>
       <c r="R19" t="n">
-        <v>6671654</v>
+        <v>6671791</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2834,12 +2804,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2848,39 +2818,43 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>förrötad granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126301457</t>
+          <t>https://artportalen.se/Sighting/137471387</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127819880</v>
+        <v>129846293</v>
       </c>
       <c r="B20" t="n">
-        <v>92632</v>
+        <v>96708</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2888,40 +2862,49 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>535002</v>
+        <v>535006</v>
       </c>
       <c r="R20" t="n">
-        <v>6671760</v>
+        <v>6671790</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2945,12 +2928,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2963,50 +2946,45 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>marken</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127819880</t>
+          <t>https://artportalen.se/Sighting/129846293</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129846284</v>
+        <v>137471373</v>
       </c>
       <c r="B21" t="n">
-        <v>92632</v>
+        <v>96646</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3014,40 +2992,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>2812</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gladtjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534990</v>
+        <v>534971</v>
       </c>
       <c r="R21" t="n">
-        <v>6671767</v>
+        <v>6671786</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3071,12 +3046,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,113 +3060,88 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129846284</t>
+          <t>https://artportalen.se/Sighting/137471373</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127820111</v>
+        <v>126301457</v>
       </c>
       <c r="B22" t="n">
-        <v>93215</v>
+        <v>97231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4368</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>535006</v>
+        <v>534778</v>
       </c>
       <c r="R22" t="n">
-        <v>6671736</v>
+        <v>6671654</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3215,12 +3165,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3233,30 +3183,35 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127820111</t>
+          <t>https://artportalen.se/Sighting/126301457</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119294755</v>
+        <v>127819880</v>
       </c>
       <c r="B23" t="n">
-        <v>92869</v>
+        <v>92632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,37 +3219,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534906</v>
+        <v>535002</v>
       </c>
       <c r="R23" t="n">
-        <v>6671703</v>
+        <v>6671760</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3318,12 +3276,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3332,33 +3290,54 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294755</t>
+          <t>https://artportalen.se/Sighting/127819880</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119889108</v>
+        <v>129846284</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>92632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3366,46 +3345,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534842</v>
+        <v>534990</v>
       </c>
       <c r="R24" t="n">
-        <v>6671768</v>
+        <v>6671767</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3429,22 +3402,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3453,71 +3416,113 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889108</t>
+          <t>https://artportalen.se/Sighting/129846284</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121853351</v>
+        <v>127820111</v>
       </c>
       <c r="B25" t="n">
-        <v>91872</v>
+        <v>93215</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>4368</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535076</v>
+        <v>535006</v>
       </c>
       <c r="R25" t="n">
-        <v>6671855</v>
+        <v>6671736</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3541,17 +3546,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gysinge Skog naturvärdesbedömning.</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3560,89 +3560,72 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>äldre granskog med tjock mossmatta</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121853351</t>
+          <t>https://artportalen.se/Sighting/127820111</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109971233</v>
+        <v>119294755</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>92869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534809</v>
+        <v>534906</v>
       </c>
       <c r="R26" t="n">
-        <v>6671806</v>
+        <v>6671703</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3666,17 +3649,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>hackspår i gammal gran</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3691,67 +3669,71 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Bengt Lundborg</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109971233</t>
+          <t>https://artportalen.se/Sighting/119294755</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121853330</v>
+        <v>119889108</v>
       </c>
       <c r="B27" t="n">
-        <v>57953</v>
+        <v>92869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534807</v>
+        <v>534842</v>
       </c>
       <c r="R27" t="n">
-        <v>6671801</v>
+        <v>6671768</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3778,17 +3760,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gysinge Skog naturvärdesbedömning.</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3799,83 +3786,69 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>gammal barrblandskog med tjock mossmatta</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121853330</t>
+          <t>https://artportalen.se/Sighting/119889108</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136976803</v>
+        <v>121853351</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Knapptjärn, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534873</v>
+        <v>535076</v>
       </c>
       <c r="R28" t="n">
-        <v>6671716</v>
+        <v>6671855</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3899,27 +3872,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:23</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:23</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Bedömdes som äldre hackspår, troligen från tretåig hackspett.</t>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3930,73 +3893,79 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>äldre granskog med tjock mossmatta</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136976803</t>
+          <t>https://artportalen.se/Sighting/121853351</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136976804</v>
+        <v>137471372</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>92148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Knapptjärn, Dlr</t>
+          <t>Gladtjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534931</v>
+        <v>534972</v>
       </c>
       <c r="R29" t="n">
-        <v>6671791</v>
+        <v>6671795</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4020,27 +3989,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:36</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bedöms som äldre hackspår, troligen frän tretåig hackspett.</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4051,69 +4005,87 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>förrötad granlåga</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136976804</t>
+          <t>https://artportalen.se/Sighting/137471372</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119889464</v>
+        <v>109971233</v>
       </c>
       <c r="B30" t="n">
-        <v>99035</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534747</v>
+        <v>534809</v>
       </c>
       <c r="R30" t="n">
-        <v>6671800</v>
+        <v>6671806</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4137,22 +4109,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>hackspår i gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4167,73 +4134,70 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889464</t>
+          <t>https://artportalen.se/Sighting/109971233</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>88075747</v>
+        <v>121853330</v>
       </c>
       <c r="B31" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gölbäcken Smedjebacken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534996</v>
+        <v>534807</v>
       </c>
       <c r="R31" t="n">
-        <v>6671715</v>
+        <v>6671801</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4257,22 +4221,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-09-19</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-09-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4281,81 +4240,82 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog med tjock mossmatta</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lena Stigsdotter</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lena Stigsdotter</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88075747</t>
+          <t>https://artportalen.se/Sighting/121853330</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109971207</v>
+        <v>136976803</v>
       </c>
       <c r="B32" t="n">
-        <v>99118</v>
+        <v>58035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>534791</v>
+        <v>534873</v>
       </c>
       <c r="R32" t="n">
-        <v>6671816</v>
+        <v>6671716</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4382,12 +4342,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bedömdes som äldre hackspår, troligen från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4396,82 +4371,75 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>naturskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Bengt Lundborg</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109971207</t>
+          <t>https://artportalen.se/Sighting/136976803</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119294425</v>
+        <v>136976804</v>
       </c>
       <c r="B33" t="n">
-        <v>99118</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>534910</v>
+        <v>534931</v>
       </c>
       <c r="R33" t="n">
-        <v>6671796</v>
+        <v>6671791</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4495,12 +4463,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bedöms som äldre hackspår, troligen frän tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4515,65 +4498,66 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294425</t>
+          <t>https://artportalen.se/Sighting/136976804</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119295534</v>
+        <v>137471390</v>
       </c>
       <c r="B34" t="n">
-        <v>99118</v>
+        <v>58035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gladtjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>534987</v>
+        <v>534822</v>
       </c>
       <c r="R34" t="n">
-        <v>6671767</v>
+        <v>6671788</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4597,12 +4581,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4613,66 +4597,76 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119295534</t>
+          <t>https://artportalen.se/Sighting/137471390</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119295577</v>
+        <v>119889464</v>
       </c>
       <c r="B35" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>534982</v>
+        <v>534747</v>
       </c>
       <c r="R35" t="n">
-        <v>6671760</v>
+        <v>6671800</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4699,12 +4693,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4719,24 +4723,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119295577</t>
+          <t>https://artportalen.se/Sighting/119889464</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119295583</v>
+        <v>88075747</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4764,20 +4768,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken Smedjebacken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>534962</v>
+        <v>534996</v>
       </c>
       <c r="R36" t="n">
-        <v>6671760</v>
+        <v>6671715</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4801,12 +4813,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2020-09-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2020-09-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4815,30 +4837,31 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Lena Stigsdotter</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Lena Stigsdotter</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119295583</t>
+          <t>https://artportalen.se/Sighting/88075747</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119888281</v>
+        <v>109971207</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4866,20 +4889,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>534939</v>
+        <v>534791</v>
       </c>
       <c r="R37" t="n">
-        <v>6671725</v>
+        <v>6671816</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4903,22 +4938,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4927,30 +4952,41 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>naturskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119888281</t>
+          <t>https://artportalen.se/Sighting/109971207</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119888431</v>
+        <v>119294425</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4981,17 +5017,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>534953</v>
+        <v>534910</v>
       </c>
       <c r="R38" t="n">
-        <v>6671754</v>
+        <v>6671796</v>
       </c>
       <c r="S38" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5015,27 +5051,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Knärot precis invid markeringen för avverkning vägen genom nyckelbiotopen.</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5050,24 +5071,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119888431</t>
+          <t>https://artportalen.se/Sighting/119294425</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119889221</v>
+        <v>119295534</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -5096,21 +5117,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>534821</v>
+        <v>534987</v>
       </c>
       <c r="R39" t="n">
-        <v>6671773</v>
+        <v>6671767</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5137,22 +5153,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5167,24 +5173,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889221</t>
+          <t>https://artportalen.se/Sighting/119295534</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119889427</v>
+        <v>119295577</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -5215,14 +5221,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gölbäcken, Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>534759</v>
+        <v>534982</v>
       </c>
       <c r="R40" t="n">
-        <v>6671790</v>
+        <v>6671760</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5249,22 +5255,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5279,24 +5275,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889427</t>
+          <t>https://artportalen.se/Sighting/119295577</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119889540</v>
+        <v>119295583</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5327,17 +5323,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>534957</v>
+        <v>534962</v>
       </c>
       <c r="R41" t="n">
-        <v>6671726</v>
+        <v>6671760</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5361,22 +5357,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5391,24 +5377,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889540</t>
+          <t>https://artportalen.se/Sighting/119295583</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119889607</v>
+        <v>119888281</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5439,17 +5425,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>534983</v>
+        <v>534939</v>
       </c>
       <c r="R42" t="n">
-        <v>6671688</v>
+        <v>6671725</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5478,7 +5464,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5488,7 +5474,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5503,24 +5489,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119889607</t>
+          <t>https://artportalen.se/Sighting/119888281</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119927799</v>
+        <v>119888431</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5549,23 +5535,19 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>534969</v>
+        <v>534953</v>
       </c>
       <c r="R43" t="n">
-        <v>6671737</v>
+        <v>6671754</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5592,42 +5574,56 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Knärot precis invid markeringen för avverkning vägen genom nyckelbiotopen.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119927799</t>
+          <t>https://artportalen.se/Sighting/119888431</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119927817</v>
+        <v>119889221</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5656,23 +5652,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>534963</v>
+        <v>534821</v>
       </c>
       <c r="R44" t="n">
-        <v>6671740</v>
+        <v>6671773</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5699,42 +5696,51 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119927817</t>
+          <t>https://artportalen.se/Sighting/119889221</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121853329</v>
+        <v>119889427</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5765,14 +5771,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>534801</v>
+        <v>534759</v>
       </c>
       <c r="R45" t="n">
-        <v>6671794</v>
+        <v>6671790</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5799,17 +5805,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gysinge Skog naturvärdesbedömning.</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5820,33 +5831,28 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>gammal barrblandskog med tjock mossmatta</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121853329</t>
+          <t>https://artportalen.se/Sighting/119889427</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125831076</v>
+        <v>119889540</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5875,23 +5881,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>534962</v>
+        <v>534957</v>
       </c>
       <c r="R46" t="n">
-        <v>6671779</v>
+        <v>6671726</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5915,12 +5917,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5929,41 +5941,30 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>grov mossig granlåga</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125831076</t>
+          <t>https://artportalen.se/Sighting/119889540</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127819624</v>
+        <v>119889607</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -5991,29 +5992,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>535048</v>
+        <v>534983</v>
       </c>
       <c r="R47" t="n">
-        <v>6671847</v>
+        <v>6671688</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6040,12 +6029,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6054,31 +6053,30 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Alec Bailey</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127819624</t>
+          <t>https://artportalen.se/Sighting/119889607</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127819733</v>
+        <v>119927799</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -6106,32 +6104,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gölbäckens gammalskog, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>535016</v>
+        <v>534969</v>
       </c>
       <c r="R48" t="n">
-        <v>6671800</v>
+        <v>6671737</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6155,12 +6145,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6176,27 +6166,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alec Bailey, Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127819733</t>
+          <t>https://artportalen.se/Sighting/119927799</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136091903</v>
+        <v>119927817</v>
       </c>
       <c r="B49" t="n">
-        <v>99346</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6232,10 +6222,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>534757</v>
+        <v>534963</v>
       </c>
       <c r="R49" t="n">
-        <v>6671803</v>
+        <v>6671740</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6262,12 +6252,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6280,35 +6270,30 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136091903</t>
+          <t>https://artportalen.se/Sighting/119927817</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136092022</v>
+        <v>121853329</v>
       </c>
       <c r="B50" t="n">
-        <v>99346</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6333,32 +6318,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>534973</v>
+        <v>534801</v>
       </c>
       <c r="R50" t="n">
-        <v>6671751</v>
+        <v>6671794</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6382,17 +6355,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>tre ynkliga plantor. Verkar vara hämmade av torkan. Platsen snitslad som hänsynsyta på radie av 8 meter.</t>
+          <t>Gysinge Skog naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6401,39 +6374,38 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog med tjock mossmatta</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136092022</t>
+          <t>https://artportalen.se/Sighting/121853329</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136976805</v>
+        <v>125831076</v>
       </c>
       <c r="B51" t="n">
-        <v>99431</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6458,26 +6430,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Knapptjärn, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>534941</v>
+        <v>534962</v>
       </c>
       <c r="R51" t="n">
-        <v>6671780</v>
+        <v>6671779</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6504,27 +6471,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:43</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Cirka 30 m till hyggesgräns. På liten yta 2x2. dm</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6533,75 +6485,94 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>grov mossig granlåga</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136976805</t>
+          <t>https://artportalen.se/Sighting/125831076</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125830803</v>
+        <v>127819624</v>
       </c>
       <c r="B52" t="n">
-        <v>102241</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>534901</v>
+        <v>535048</v>
       </c>
       <c r="R52" t="n">
-        <v>6671688</v>
+        <v>6671847</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6625,12 +6596,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6643,76 +6614,80 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Janolof Hermansson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830803</t>
+          <t>https://artportalen.se/Sighting/127819624</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>67601802</v>
+        <v>127819733</v>
       </c>
       <c r="B53" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
+          <t>Gölbäckens gammalskog, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>534847</v>
+        <v>535016</v>
       </c>
       <c r="R53" t="n">
-        <v>6671789</v>
+        <v>6671800</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6736,12 +6711,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2017-09-17</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2017-09-17</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6750,81 +6725,76 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>litet klibbalkärr</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67601802</t>
+          <t>https://artportalen.se/Sighting/127819733</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119294603</v>
+        <v>136091903</v>
       </c>
       <c r="B54" t="n">
-        <v>104628</v>
+        <v>99346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>534885</v>
+        <v>534757</v>
       </c>
       <c r="R54" t="n">
-        <v>6671725</v>
+        <v>6671803</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6848,12 +6818,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6862,72 +6832,86 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294603</t>
+          <t>https://artportalen.se/Sighting/136091903</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125830603</v>
+        <v>136092022</v>
       </c>
       <c r="B55" t="n">
-        <v>104628</v>
+        <v>99346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>535006</v>
+        <v>534973</v>
       </c>
       <c r="R55" t="n">
-        <v>6671720</v>
+        <v>6671751</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6954,12 +6938,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>tre ynkliga plantor. Verkar vara hämmade av torkan. Platsen snitslad som hänsynsyta på radie av 8 meter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6974,12 +6963,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>nära bäcken</t>
+          <t>Lågörtbarrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6990,61 +6974,66 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830603</t>
+          <t>https://artportalen.se/Sighting/136092022</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125830789</v>
+        <v>136976805</v>
       </c>
       <c r="B56" t="n">
-        <v>104628</v>
+        <v>99434</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>534901</v>
+        <v>534941</v>
       </c>
       <c r="R56" t="n">
-        <v>6671688</v>
+        <v>6671780</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7071,12 +7060,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Cirka 30 m till hyggesgräns. På liten yta 2x2. dm</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7085,74 +7089,72 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830789</t>
+          <t>https://artportalen.se/Sighting/136976805</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136976802</v>
+        <v>125830803</v>
       </c>
       <c r="B57" t="n">
-        <v>104965</v>
+        <v>102241</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Knapptjärn, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>534873</v>
+        <v>534901</v>
       </c>
       <c r="R57" t="n">
-        <v>6671716</v>
+        <v>6671688</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7179,27 +7181,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>16:17</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kvar på hygge som torkar ut.</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7208,33 +7195,39 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136976802</t>
+          <t>https://artportalen.se/Sighting/125830803</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136976806</v>
+        <v>67601802</v>
       </c>
       <c r="B58" t="n">
-        <v>104965</v>
+        <v>97983</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7242,16 +7235,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7260,19 +7253,22 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Knapptjärn, Dlr</t>
+          <t>Gölbäcken, O om Knapptjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>534986</v>
+        <v>534847</v>
       </c>
       <c r="R58" t="n">
-        <v>6671759</v>
+        <v>6671789</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7296,22 +7292,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2017-09-17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2017-09-17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7322,31 +7308,41 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>litet klibbalkärr</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136976806</t>
+          <t>https://artportalen.se/Sighting/67601802</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118074415</v>
+        <v>119294603</v>
       </c>
       <c r="B59" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7354,41 +7350,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Knapptjärn, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>534955</v>
+        <v>534885</v>
       </c>
       <c r="R59" t="n">
-        <v>6671722</v>
+        <v>6671725</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7412,12 +7404,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7426,34 +7418,33 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Åke Persson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118074415</t>
+          <t>https://artportalen.se/Sighting/119294603</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119057996</v>
+        <v>125830603</v>
       </c>
       <c r="B60" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7461,21 +7452,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7485,14 +7476,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gölbäcken - Kapptjärn, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>534905</v>
+        <v>535006</v>
       </c>
       <c r="R60" t="n">
-        <v>6671685</v>
+        <v>6671720</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7519,12 +7510,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7542,6 +7533,11 @@
           <t>Lågörtgranskog</t>
         </is>
       </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>nära bäcken</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
@@ -7550,22 +7546,22 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119057996</t>
+          <t>https://artportalen.se/Sighting/125830603</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119294689</v>
+        <v>125830789</v>
       </c>
       <c r="B61" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7573,37 +7569,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>534895</v>
+        <v>534901</v>
       </c>
       <c r="R61" t="n">
-        <v>6671684</v>
+        <v>6671688</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7627,12 +7627,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7641,33 +7641,39 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Stig-Åke Svenson</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119294689</t>
+          <t>https://artportalen.se/Sighting/125830789</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119927788</v>
+        <v>136976802</v>
       </c>
       <c r="B62" t="n">
-        <v>101326</v>
+        <v>104968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7675,38 +7681,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>534956</v>
+        <v>534873</v>
       </c>
       <c r="R62" t="n">
-        <v>6671735</v>
+        <v>6671716</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7733,12 +7735,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Kvar på hygge som torkar ut.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7747,34 +7764,33 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119927788</t>
+          <t>https://artportalen.se/Sighting/136976802</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125830768</v>
+        <v>136976806</v>
       </c>
       <c r="B63" t="n">
-        <v>101326</v>
+        <v>104968</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7782,41 +7798,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gölbäcken - Knapptjärn, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>534901</v>
+        <v>534986</v>
       </c>
       <c r="R63" t="n">
-        <v>6671688</v>
+        <v>6671759</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7840,12 +7852,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7854,36 +7876,30 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Åke Persson</t>
+          <t>Cecilia Rastad, Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125830768</t>
+          <t>https://artportalen.se/Sighting/136976806</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126301498</v>
+        <v>118074415</v>
       </c>
       <c r="B64" t="n">
         <v>101326</v>
@@ -7918,14 +7934,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>534879</v>
+        <v>534955</v>
       </c>
       <c r="R64" t="n">
-        <v>6671662</v>
+        <v>6671722</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7952,17 +7968,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Inom kulturmijöhänsyn</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7975,35 +7986,30 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126301498</t>
+          <t>https://artportalen.se/Sighting/118074415</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136091964</v>
+        <v>119057996</v>
       </c>
       <c r="B65" t="n">
-        <v>101556</v>
+        <v>101326</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8035,14 +8041,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Gölbäcken - Kapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>534902</v>
+        <v>534905</v>
       </c>
       <c r="R65" t="n">
-        <v>6671682</v>
+        <v>6671685</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8069,12 +8075,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8089,7 +8095,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8100,22 +8106,22 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136091964</t>
+          <t>https://artportalen.se/Sighting/119057996</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136091947</v>
+        <v>119294689</v>
       </c>
       <c r="B66" t="n">
-        <v>99623</v>
+        <v>101326</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8123,41 +8129,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gölbäcken, Dlr</t>
+          <t>Fräkenkärret, Fräkenkärret, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>534900</v>
+        <v>534895</v>
       </c>
       <c r="R66" t="n">
-        <v>6671688</v>
+        <v>6671684</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8181,12 +8183,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8195,39 +8197,33 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Patric Engfeldt, Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136091947</t>
+          <t>https://artportalen.se/Sighting/119294689</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126301411</v>
+        <v>119927788</v>
       </c>
       <c r="B67" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8235,19 +8231,23 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -8255,14 +8255,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>534748</v>
+        <v>534956</v>
       </c>
       <c r="R67" t="n">
-        <v>6671807</v>
+        <v>6671735</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8289,12 +8289,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8307,35 +8307,30 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126301411</t>
+          <t>https://artportalen.se/Sighting/119927788</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126301477</v>
+        <v>125830768</v>
       </c>
       <c r="B68" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8343,19 +8338,23 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -8363,14 +8362,14 @@
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Knapptjärn/Gölbäcken, Dlr</t>
+          <t>Gölbäcken - Knapptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>534789</v>
+        <v>534901</v>
       </c>
       <c r="R68" t="n">
-        <v>6671626</v>
+        <v>6671688</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8397,17 +8396,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8422,7 +8416,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8433,11 +8427,573 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Åke Persson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125830768</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126301498</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>534879</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6671662</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Inom kulturmijöhänsyn</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126301498</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136091964</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101556</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>534902</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6671682</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136091964</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>136091947</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99623</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>534900</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6671688</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136091947</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126301411</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>534748</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6671807</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126301411</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126301477</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Knapptjärn/Gölbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>534789</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6671626</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126301477</t>
         </is>
@@ -8512,6 +9068,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>136976805</v>
       </c>
       <c r="B56" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136976802</v>
       </c>
       <c r="B62" t="n">
-        <v>104968</v>
+        <v>104970</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136976806</v>
       </c>
       <c r="B63" t="n">
-        <v>104968</v>
+        <v>104970</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 57321-2024 artfynd.xlsx
+++ b/artfynd/A 57321-2024 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>136976807</v>
       </c>
       <c r="B8" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>137471394</v>
       </c>
       <c r="B14" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>137471387</v>
       </c>
       <c r="B19" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>137471373</v>
       </c>
       <c r="B21" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>137471372</v>
       </c>
       <c r="B29" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>136976803</v>
       </c>
       <c r="B32" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>136976804</v>
       </c>
       <c r="B33" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>137471390</v>
       </c>
       <c r="B34" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>136976805</v>
       </c>
       <c r="B56" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136976802</v>
       </c>
       <c r="B62" t="n">
-        <v>104970</v>
+        <v>104974</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136976806</v>
       </c>
       <c r="B63" t="n">
-        <v>104970</v>
+        <v>104974</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
